--- a/docs/CDM/common_datamodel.xlsx
+++ b/docs/CDM/common_datamodel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saros\Documents\ATLAS\atlas_cardio\github_repo\atlas-cardio\docs\CDM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F325BE25-EDC0-4F9E-9D31-93A99836D430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23516FA4-0B96-4CB1-9DF1-AB3931457866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4125" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3079" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="1362">
   <si>
     <t>Project</t>
   </si>
@@ -3073,7 +3073,1054 @@
     <t>Coordinador de calidad del sector sanitario de Alcañiz</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>AtlasVPM Cardio: Atención ambulatoria en la enfermedad cardíaca</t>
+  </si>
+  <si>
+    <t>I11</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca hipertensiva</t>
+  </si>
+  <si>
+    <t>Enfermedad cardíaca hipertensiva con insuficiencia cardiaca</t>
+  </si>
+  <si>
+    <t>I11.9</t>
+  </si>
+  <si>
+    <t>I119</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca hipertensiva sin insuficiencia cardiaca</t>
+  </si>
+  <si>
+    <t>I13</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva con insuficiencia cardiaca y enfermedad renal crónica estadios 1 a 4 o enfermedad renal crónica no especificada</t>
+  </si>
+  <si>
+    <t>I13.1</t>
+  </si>
+  <si>
+    <t>I131</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva sin insuficiencia cardiaca</t>
+  </si>
+  <si>
+    <t>I13.10</t>
+  </si>
+  <si>
+    <t>I1310</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva sin insuficiencia cardiaca, con enfermedad renal crónica en estadio 1 a 4 o enfermedad renal crónica no especificada</t>
+  </si>
+  <si>
+    <t>I13.11</t>
+  </si>
+  <si>
+    <t>I1311</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva sin insuficiencia cardiaca con enfermedad renal crónica en estadio 5 o con enfermedad renal en estadio terminal</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca y renal crónica hipertensiva con insuficiencia cardiaca y con enfermedad renal crónica en estadio 5 o con enfermedad renal en estadio terminal</t>
+  </si>
+  <si>
+    <t>I20</t>
+  </si>
+  <si>
+    <t>I20.2</t>
+  </si>
+  <si>
+    <t>I202</t>
+  </si>
+  <si>
+    <t>Angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I21</t>
+  </si>
+  <si>
+    <t>I21.01</t>
+  </si>
+  <si>
+    <t>I2101</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de arteria coronaria principal izquierda</t>
+  </si>
+  <si>
+    <t>I21.02</t>
+  </si>
+  <si>
+    <t>I2102</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de arteria coronaria descendente anterior</t>
+  </si>
+  <si>
+    <t>I21.09</t>
+  </si>
+  <si>
+    <t>I2109</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de otra arteria coronaria de la cara anterior</t>
+  </si>
+  <si>
+    <t>I21.11</t>
+  </si>
+  <si>
+    <t>I2111</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de arteria coronaria derecha</t>
+  </si>
+  <si>
+    <t>I21.19</t>
+  </si>
+  <si>
+    <t>I2119</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de otra arteria coronaria de cara inferior</t>
+  </si>
+  <si>
+    <t>I21.21</t>
+  </si>
+  <si>
+    <t>I2121</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) con implicación de la arteria coronaria circunfleja</t>
+  </si>
+  <si>
+    <t>I21.29</t>
+  </si>
+  <si>
+    <t>I2129</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio con elevación de ST (IAMCEST) (IMEST) (STEMI) de otra localización</t>
+  </si>
+  <si>
+    <t>I21.A</t>
+  </si>
+  <si>
+    <t>I21A</t>
+  </si>
+  <si>
+    <t>Otro tipo de infarto de miocardio</t>
+  </si>
+  <si>
+    <t>I21.A1</t>
+  </si>
+  <si>
+    <t>I21A1</t>
+  </si>
+  <si>
+    <t>Infarto de miocardio tipo 2</t>
+  </si>
+  <si>
+    <t>I21.A9</t>
+  </si>
+  <si>
+    <t>I21A9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Otro tipo de infarto de miocardio</t>
+  </si>
+  <si>
+    <t>I22</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio subsiguiente con elevación de ST (IAMCEST) (IMEST) (STEMI) y sin elevación de ST (IAMSEST) (IMNEST) (NSTEMI)</t>
+  </si>
+  <si>
+    <t>I22.2</t>
+  </si>
+  <si>
+    <t>I222</t>
+  </si>
+  <si>
+    <t>Infarto agudo de miocardio subsiguiente sin elevación de ST (IMSEST) (IMNEST) (NSTEMI)</t>
+  </si>
+  <si>
+    <t>I23</t>
+  </si>
+  <si>
+    <t>Complicaciones en curso, tras infarto de miocardio con elevación de ST (IAMCEST)(IMEST)(STEMI) y sin elevación del ST (IAMSEST)(IMSEST)(NSTEMI) (dentro del periodo de 28 días)</t>
+  </si>
+  <si>
+    <t>I23.0</t>
+  </si>
+  <si>
+    <t>I230</t>
+  </si>
+  <si>
+    <t>Hemopericardio como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.1</t>
+  </si>
+  <si>
+    <t>I231</t>
+  </si>
+  <si>
+    <t>Defecto de tabique auricular como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.2</t>
+  </si>
+  <si>
+    <t>I232</t>
+  </si>
+  <si>
+    <t>Defecto de tabique ventricular como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.3</t>
+  </si>
+  <si>
+    <t>I233</t>
+  </si>
+  <si>
+    <t>Rotura de pared cardiaca sin hemopericardio como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.4</t>
+  </si>
+  <si>
+    <t>I234</t>
+  </si>
+  <si>
+    <t>Rotura de cuerdas tendinosas como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.5</t>
+  </si>
+  <si>
+    <t>I235</t>
+  </si>
+  <si>
+    <t>Rotura de músculo papilar como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.6</t>
+  </si>
+  <si>
+    <t>I236</t>
+  </si>
+  <si>
+    <t>Trombosis de aurícula, orejuela y ventrículo como complicación actual tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I23.7</t>
+  </si>
+  <si>
+    <t>I237</t>
+  </si>
+  <si>
+    <t>Angina posinfarto</t>
+  </si>
+  <si>
+    <t>I23.8</t>
+  </si>
+  <si>
+    <t>I238</t>
+  </si>
+  <si>
+    <t>Otras complicaciones actuales tras infarto agudo de miocardio</t>
+  </si>
+  <si>
+    <t>I24</t>
+  </si>
+  <si>
+    <t>Otras enfermedades isquémicas agudas cardiacas</t>
+  </si>
+  <si>
+    <t>I25</t>
+  </si>
+  <si>
+    <t>Enfermedad isquémica crónica cardiaca</t>
+  </si>
+  <si>
+    <t>I25.10</t>
+  </si>
+  <si>
+    <t>I2510</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa sin angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.11</t>
+  </si>
+  <si>
+    <t>I2511</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.110</t>
+  </si>
+  <si>
+    <t>I25110</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.111</t>
+  </si>
+  <si>
+    <t>I25111</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.112</t>
+  </si>
+  <si>
+    <t>I25112</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.118</t>
+  </si>
+  <si>
+    <t>I25118</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.119</t>
+  </si>
+  <si>
+    <t>I25119</t>
+  </si>
+  <si>
+    <t>Enfermedad cardiaca aterosclerótica de arteria coronaria nativa con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.41</t>
+  </si>
+  <si>
+    <t>I2541</t>
+  </si>
+  <si>
+    <t>Aneurisma de arteria coronaria</t>
+  </si>
+  <si>
+    <t>I25.42</t>
+  </si>
+  <si>
+    <t>I2542</t>
+  </si>
+  <si>
+    <t>Disección de arteria coronaria</t>
+  </si>
+  <si>
+    <t>I25.70</t>
+  </si>
+  <si>
+    <t>I2570</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.700</t>
+  </si>
+  <si>
+    <t>I25700</t>
+  </si>
+  <si>
+    <t> Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.701</t>
+  </si>
+  <si>
+    <t>I25701</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.702</t>
+  </si>
+  <si>
+    <t>I25702</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.708</t>
+  </si>
+  <si>
+    <t>I25708</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.709</t>
+  </si>
+  <si>
+    <t>I25709</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria, no especificado, con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.71</t>
+  </si>
+  <si>
+    <t>I2571</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria, con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.710</t>
+  </si>
+  <si>
+    <t>I25710</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.711</t>
+  </si>
+  <si>
+    <t>I25711</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.712</t>
+  </si>
+  <si>
+    <t>I25712</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria, con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.718</t>
+  </si>
+  <si>
+    <t>I25718</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.719</t>
+  </si>
+  <si>
+    <t>I25719</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) venoso autólogo de derivación de arteria coronaria, con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.72</t>
+  </si>
+  <si>
+    <t>I2572</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria, con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.720</t>
+  </si>
+  <si>
+    <t>I25720</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria, con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.721</t>
+  </si>
+  <si>
+    <t>I25721</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria, con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.722</t>
+  </si>
+  <si>
+    <t>I25722</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria, con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.728</t>
+  </si>
+  <si>
+    <t>I25728</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.729</t>
+  </si>
+  <si>
+    <t>I25729</t>
+  </si>
+  <si>
+    <t>Ateroesclerosis de injerto(s) arterial autólogo de derivación de arteria coronaria con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.73</t>
+  </si>
+  <si>
+    <t>I2573</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.730</t>
+  </si>
+  <si>
+    <t>I25730</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.731</t>
+  </si>
+  <si>
+    <t>I25731</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.732</t>
+  </si>
+  <si>
+    <t>I25732</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.738</t>
+  </si>
+  <si>
+    <t>I25738</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.739</t>
+  </si>
+  <si>
+    <t>I25739</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) biológico no autólogo de derivación de arteria coronaria con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.75</t>
+  </si>
+  <si>
+    <t>I2575</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.750</t>
+  </si>
+  <si>
+    <t>I25750</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con angina inestable</t>
+  </si>
+  <si>
+    <t>I25.751</t>
+  </si>
+  <si>
+    <t>I25751</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.752</t>
+  </si>
+  <si>
+    <t>I25752</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.758</t>
+  </si>
+  <si>
+    <t>I25758</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.759</t>
+  </si>
+  <si>
+    <t>I25759</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.76</t>
+  </si>
+  <si>
+    <t>I2576</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.760</t>
+  </si>
+  <si>
+    <t>I25760</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con angina inestable</t>
+  </si>
+  <si>
+    <t>I25.761</t>
+  </si>
+  <si>
+    <t>I25761</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.762</t>
+  </si>
+  <si>
+    <t>I25762</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.768</t>
+  </si>
+  <si>
+    <t>I25768</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.769</t>
+  </si>
+  <si>
+    <t>I25769</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria de corazón trasplantado con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.79</t>
+  </si>
+  <si>
+    <t>I2579</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.790</t>
+  </si>
+  <si>
+    <t>I25790</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con angina de pecho inestable</t>
+  </si>
+  <si>
+    <t>I25.791</t>
+  </si>
+  <si>
+    <t>I25791</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con angina de pecho con espasmo documentado</t>
+  </si>
+  <si>
+    <t>I25.792</t>
+  </si>
+  <si>
+    <t>I25792</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con angina de pecho refractaria</t>
+  </si>
+  <si>
+    <t>I25.798</t>
+  </si>
+  <si>
+    <t>I25798</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con otras formas de angina de pecho</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otro tipo de injerto(s) de derivación de arteria coronaria con angina de pecho no especificada</t>
+  </si>
+  <si>
+    <t>I25.81</t>
+  </si>
+  <si>
+    <t>I2581</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de otros vasos coronarios sin angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.810</t>
+  </si>
+  <si>
+    <t>I25810</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto(s) de derivación de arteria coronaria sin angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.811</t>
+  </si>
+  <si>
+    <t>I25811</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de arteria coronaria nativa de corazón trasplantado sin angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.812</t>
+  </si>
+  <si>
+    <t>I25812</t>
+  </si>
+  <si>
+    <t>Aterosclerosis de injerto de derivación de arteria coronaria de corazón trasplantado sin angina de pecho</t>
+  </si>
+  <si>
+    <t>I25.82</t>
+  </si>
+  <si>
+    <t>I2582</t>
+  </si>
+  <si>
+    <t>Oclusión total crónica de arteria coronaria</t>
+  </si>
+  <si>
+    <t>I25.83</t>
+  </si>
+  <si>
+    <t>I2583</t>
+  </si>
+  <si>
+    <t>Aterosclerosis coronaria debida a placa rica en lípidos</t>
+  </si>
+  <si>
+    <t>I25.84</t>
+  </si>
+  <si>
+    <t>I2584</t>
+  </si>
+  <si>
+    <t>Aterosclerosis coronaria debida a lesión coronaria calcificada</t>
+  </si>
+  <si>
+    <t>I25.89</t>
+  </si>
+  <si>
+    <t>I2589</t>
+  </si>
+  <si>
+    <t>Otras formas de enfermedad isquémica crónica cardiaca</t>
+  </si>
+  <si>
+    <t>I48</t>
+  </si>
+  <si>
+    <t>Fibrilación y flutter auricular</t>
+  </si>
+  <si>
+    <t>I48.1</t>
+  </si>
+  <si>
+    <t>I481</t>
+  </si>
+  <si>
+    <t>Fibrilación auricular persistente</t>
+  </si>
+  <si>
+    <t>I48.2</t>
+  </si>
+  <si>
+    <t>I482</t>
+  </si>
+  <si>
+    <t>Fibrilación auricular crónica</t>
+  </si>
+  <si>
+    <t>I48.9</t>
+  </si>
+  <si>
+    <t>I489</t>
+  </si>
+  <si>
+    <t>Fibrilación y flutter auriculares no especificados</t>
+  </si>
+  <si>
+    <t>I50</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca</t>
+  </si>
+  <si>
+    <t>I50.20</t>
+  </si>
+  <si>
+    <t>I5020</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca sistólica (congestiva), no especificada</t>
+  </si>
+  <si>
+    <t>I50.21</t>
+  </si>
+  <si>
+    <t>I5021</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca sistólica (congestiva), aguda</t>
+  </si>
+  <si>
+    <t>I50.22</t>
+  </si>
+  <si>
+    <t>I5022</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca sistólica (congestiva), crónica</t>
+  </si>
+  <si>
+    <t>I50.23</t>
+  </si>
+  <si>
+    <t>I5023</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca sistólica (congestiva), aguda sobre crónica</t>
+  </si>
+  <si>
+    <t>I50.30</t>
+  </si>
+  <si>
+    <t>I5030</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca diastólica (congestiva), no especificada</t>
+  </si>
+  <si>
+    <t>I50.31</t>
+  </si>
+  <si>
+    <t>I5031</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca diastólica (congestiva), aguda</t>
+  </si>
+  <si>
+    <t>I50.32</t>
+  </si>
+  <si>
+    <t>I5032</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca diastólica (congestiva), crónica</t>
+  </si>
+  <si>
+    <t>I50.33</t>
+  </si>
+  <si>
+    <t>I5033</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardiaca diastólica (congestiva), aguda sobre crónica</t>
+  </si>
+  <si>
+    <t>I50.40</t>
+  </si>
+  <si>
+    <t>I5040</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca combinada sistólica (congestiva) y diastólica (congestiva), no especificada</t>
+  </si>
+  <si>
+    <t>I50.41</t>
+  </si>
+  <si>
+    <t>I5041</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca combinada sistólica (congestiva) y diastólica (congestiva), aguda</t>
+  </si>
+  <si>
+    <t>I50.42</t>
+  </si>
+  <si>
+    <t>I5042</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca combinada sistólica (congestiva) y diastólica (congestiva), crónica</t>
+  </si>
+  <si>
+    <t>I50.43</t>
+  </si>
+  <si>
+    <t>I5043</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca combinada sistólica (congestiva) y diastólica (congestiva), aguda sobre crónica</t>
+  </si>
+  <si>
+    <t>I50.8</t>
+  </si>
+  <si>
+    <t>I508</t>
+  </si>
+  <si>
+    <t>Otra insuficiencia cardíaca</t>
+  </si>
+  <si>
+    <t>I50.81</t>
+  </si>
+  <si>
+    <t>I5081</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha</t>
+  </si>
+  <si>
+    <t>I50.810</t>
+  </si>
+  <si>
+    <t>I50810</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha, no especificada</t>
+  </si>
+  <si>
+    <t>I50.811</t>
+  </si>
+  <si>
+    <t>I50811</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha aguda</t>
+  </si>
+  <si>
+    <t>I50.812</t>
+  </si>
+  <si>
+    <t>I50812</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha crónica</t>
+  </si>
+  <si>
+    <t>I50.813</t>
+  </si>
+  <si>
+    <t>I50813</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha aguda sobre crónica</t>
+  </si>
+  <si>
+    <t>I50.814</t>
+  </si>
+  <si>
+    <t>I50814</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca derecha por insuficiencia cardíaca izquierda</t>
+  </si>
+  <si>
+    <t>I50.82</t>
+  </si>
+  <si>
+    <t>I5082</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca biventricular</t>
+  </si>
+  <si>
+    <t>I50.83</t>
+  </si>
+  <si>
+    <t>I5083</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca de alto gasto</t>
+  </si>
+  <si>
+    <t>I50.84</t>
+  </si>
+  <si>
+    <t>I5084</t>
+  </si>
+  <si>
+    <t>Insuficiencia cardíaca en estadio terminal</t>
+  </si>
+  <si>
+    <t>I50.89</t>
+  </si>
+  <si>
+    <t>I5089</t>
+  </si>
+  <si>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>0.0.1 primera versión de modelo común de datos
@@ -3083,10 +4130,8 @@
 0.0.5 Se añade la variable 'fecha_enfermedad_dt' a la entidad paciente (pestaña 'paciente'). Se actualiza la columna 'transformations_from_origin' de la variable 'test_cd' (pestaña 'test_cd') y 'examen_cd' (pestaña 'examenes'). Se elimina la columna 'enfermedad_st' en la pestaña 'tratamiento_atc_tratamiento_cd' y del catálogo correspondiente.
 0.1.0 Se modifica la definición de la cohorte: Ampliar selección de pacientes hasta 2023-12-31. Se añaden códigos CIE-10 de Fibrilación Auricular (FA) en la pestaña 'cohort_definition_inclusion' (por lo que se añaden también en la pestaña 'paciente_enfermedad_cd' (catálogo de la variable 'enfermedad_cd' de la entidad 'paciente')). En la entidad 'paciente' se modifica en la columna 'observations_comments' las variables 'zbs_residencia_cd', 'edad_nm', 'nivel_copago_cd'. En la entidad 'población' se modifica en la columna 'observations_comments' las variables 'año_cd','zbs_residencia_cd', 'nivel_copago_cd'. En la entidad 'tratamiento' se modifica en la columna 'observations_comments' la variable 'atc_tratamiento_cd'. En la entidad 'comorbilidad' se modifica en la columna 'observations_comments' la variable 'fecha_diag_comorbilidad_dt'. En las entidades 'tratamiento' y 'comorbilidad' se corrige el 'label' de la variable 'patiente_id' y pasa a 'paciente_id'.  
 0.1.1 Actualización de los autores del modelo de datos.
-0.1.2 Actualización título del proyecto.</t>
-  </si>
-  <si>
-    <t>AtlasVPM Cardio: Atención ambulatoria en la enfermedad cardíaca</t>
+0.1.2 Actualización título del proyecto.
+0.1.3 Actualización de los códigos ICD-10 para clarificar qué códigos se deben tener en cuenta a máximo nivel de granularidad, esta modificación se ve reflejada en "cohort_definition_inclusion.csv" y en la hoja de "cohort_definition_inclusion" del Excel "common_datamodel.xlsx"</t>
   </si>
 </sst>
 </file>
@@ -3096,13 +4141,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3125,12 +4183,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3444,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3484,7 +4544,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>1011</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -3621,12 +4681,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1012</v>
+        <v>1361</v>
       </c>
     </row>
   </sheetData>
@@ -11004,8 +12064,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="34.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -11714,983 +12777,3595 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>136</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="A36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C46" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D46" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H46" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>136</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C47" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D47" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H47" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C49" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D49" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H49" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C50" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D50" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G50" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H50" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C52" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D52" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H52" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>136</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C56" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D56" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G56" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H56" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>136</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C59" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D59" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H59" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>136</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C62" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D62" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H62" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>136</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C63" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D63" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G63" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H63" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C64" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D64" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G64" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H64" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>136</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C69" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D69" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G69" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H69" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C70" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D70" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G70" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H70" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>136</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C72" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D72" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H72" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C73" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D73" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G73" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H73" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C85" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D85" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G85" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H85" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C86" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D86" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G86" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H86" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C87" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D87" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G87" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H87" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>136</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C88" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D88" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G88" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H88" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" t="s">
-        <v>191</v>
-      </c>
-      <c r="C54" t="s">
-        <v>192</v>
-      </c>
-      <c r="D54" t="s">
-        <v>193</v>
-      </c>
-      <c r="G54" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H89" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C90" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D90" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G90" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H90" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C98" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D98" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G98" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H98" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>136</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C99" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D99" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G99" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H99" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" t="s">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C100" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D100" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H100" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>136</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C103" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D103" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G103" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H103" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C104" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D104" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G104" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H104" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>136</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C105" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D105" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G105" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H105" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>136</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E139" s="3"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C148" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D148" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G148" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H148" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" t="s">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C157" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D157" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G157" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H157" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>136</v>
-      </c>
-      <c r="B64" t="s">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C158" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D158" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G64" t="s">
+      <c r="E158" s="3"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H158" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>136</v>
-      </c>
-      <c r="B65" t="s">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C159" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D159" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G65" t="s">
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H159" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>136</v>
-      </c>
-      <c r="B66" t="s">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C160" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D160" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G66" t="s">
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H160" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" t="s">
-        <v>230</v>
-      </c>
-      <c r="C67" t="s">
-        <v>231</v>
-      </c>
-      <c r="D67" t="s">
-        <v>232</v>
-      </c>
-      <c r="G67" t="s">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E161" s="3"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H174" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" t="s">
-        <v>233</v>
-      </c>
-      <c r="C68" t="s">
-        <v>234</v>
-      </c>
-      <c r="D68" t="s">
-        <v>235</v>
-      </c>
-      <c r="G68" t="s">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G175" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H175" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" t="s">
-        <v>236</v>
-      </c>
-      <c r="C69" t="s">
-        <v>237</v>
-      </c>
-      <c r="D69" t="s">
-        <v>235</v>
-      </c>
-      <c r="G69" t="s">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G176" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H176" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" t="s">
-        <v>238</v>
-      </c>
-      <c r="C70" t="s">
-        <v>239</v>
-      </c>
-      <c r="D70" t="s">
-        <v>240</v>
-      </c>
-      <c r="G70" t="s">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H177" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>136</v>
-      </c>
-      <c r="B71" t="s">
-        <v>241</v>
-      </c>
-      <c r="C71" t="s">
-        <v>242</v>
-      </c>
-      <c r="D71" t="s">
-        <v>243</v>
-      </c>
-      <c r="G71" t="s">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H178" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>136</v>
-      </c>
-      <c r="B72" t="s">
-        <v>244</v>
-      </c>
-      <c r="C72" t="s">
-        <v>245</v>
-      </c>
-      <c r="D72" t="s">
-        <v>246</v>
-      </c>
-      <c r="G72" t="s">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H179" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>136</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B181" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C181" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D181" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G181" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H181" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>136</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C186" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D186" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G186" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H186" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>136</v>
-      </c>
-      <c r="B75" t="s">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3"/>
+      <c r="G189" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E190" s="3"/>
+      <c r="F190" s="3"/>
+      <c r="G190" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E194" s="3"/>
+      <c r="F194" s="3"/>
+      <c r="G194" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E195" s="3"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E196" s="3"/>
+      <c r="F196" s="3"/>
+      <c r="G196" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E197" s="3"/>
+      <c r="F197" s="3"/>
+      <c r="G197" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E199" s="3"/>
+      <c r="F199" s="3"/>
+      <c r="G199" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E200" s="3"/>
+      <c r="F200" s="3"/>
+      <c r="G200" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E201" s="3"/>
+      <c r="F201" s="3"/>
+      <c r="G201" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B202" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C202" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D202" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G202" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H202" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>136</v>
-      </c>
-      <c r="B76" t="s">
-        <v>256</v>
-      </c>
-      <c r="C76" t="s">
-        <v>257</v>
-      </c>
-      <c r="D76" t="s">
-        <v>258</v>
-      </c>
-      <c r="G76" t="s">
-        <v>72</v>
-      </c>
-      <c r="H76" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>136</v>
-      </c>
-      <c r="B77" t="s">
-        <v>260</v>
-      </c>
-      <c r="C77" t="s">
-        <v>261</v>
-      </c>
-      <c r="D77" t="s">
-        <v>262</v>
-      </c>
-      <c r="G77" t="s">
-        <v>72</v>
-      </c>
-      <c r="H77" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>136</v>
-      </c>
-      <c r="B78" t="s">
-        <v>263</v>
-      </c>
-      <c r="C78" t="s">
-        <v>264</v>
-      </c>
-      <c r="D78" t="s">
-        <v>265</v>
-      </c>
-      <c r="G78" t="s">
-        <v>72</v>
-      </c>
-      <c r="H78" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>136</v>
-      </c>
-      <c r="B79" t="s">
-        <v>266</v>
-      </c>
-      <c r="C79" t="s">
-        <v>267</v>
-      </c>
-      <c r="D79" t="s">
-        <v>268</v>
-      </c>
-      <c r="G79" t="s">
-        <v>72</v>
-      </c>
-      <c r="H79" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B80" t="s">
-        <v>269</v>
-      </c>
-      <c r="C80" t="s">
-        <v>270</v>
-      </c>
-      <c r="D80" t="s">
-        <v>271</v>
-      </c>
-      <c r="G80" t="s">
-        <v>72</v>
-      </c>
-      <c r="H80" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>136</v>
-      </c>
-      <c r="B81" t="s">
-        <v>272</v>
-      </c>
-      <c r="C81" t="s">
-        <v>273</v>
-      </c>
-      <c r="D81" t="s">
-        <v>274</v>
-      </c>
-      <c r="G81" t="s">
-        <v>72</v>
-      </c>
-      <c r="H81" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>136</v>
-      </c>
-      <c r="B82" t="s">
-        <v>275</v>
-      </c>
-      <c r="C82" t="s">
-        <v>276</v>
-      </c>
-      <c r="D82" t="s">
-        <v>277</v>
-      </c>
-      <c r="G82" t="s">
-        <v>72</v>
-      </c>
-      <c r="H82" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>136</v>
-      </c>
-      <c r="B83" t="s">
-        <v>278</v>
-      </c>
-      <c r="C83" t="s">
-        <v>279</v>
-      </c>
-      <c r="D83" t="s">
-        <v>280</v>
-      </c>
-      <c r="G83" t="s">
-        <v>72</v>
-      </c>
-      <c r="H83" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>136</v>
-      </c>
-      <c r="B84" t="s">
-        <v>281</v>
-      </c>
-      <c r="C84" t="s">
-        <v>282</v>
-      </c>
-      <c r="D84" t="s">
-        <v>283</v>
-      </c>
-      <c r="G84" t="s">
-        <v>72</v>
-      </c>
-      <c r="H84" t="s">
-        <v>259</v>
       </c>
     </row>
   </sheetData>
